--- a/output/roomself_excel/11048.xlsx
+++ b/output/roomself_excel/11048.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>302217</v>
+        <v>94913</v>
       </c>
       <c r="D2" t="n">
-        <v>5040</v>
+        <v>2576</v>
       </c>
       <c r="E2" t="n">
-        <v>899</v>
+        <v>431</v>
       </c>
       <c r="F2" t="n">
-        <v>706</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>131084</v>
+        <v>157396</v>
       </c>
       <c r="D3" t="n">
-        <v>3044</v>
+        <v>3188</v>
       </c>
       <c r="E3" t="n">
-        <v>513</v>
+        <v>468</v>
       </c>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39298</v>
+        <v>131084</v>
       </c>
       <c r="D4" t="n">
-        <v>1624</v>
+        <v>3044</v>
       </c>
       <c r="E4" t="n">
-        <v>188</v>
+        <v>513</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18605</v>
+        <v>39298</v>
       </c>
       <c r="D5" t="n">
-        <v>1160</v>
+        <v>1624</v>
       </c>
       <c r="E5" t="n">
-        <v>331</v>
+        <v>188</v>
       </c>
       <c r="F5" t="n">
-        <v>185</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22436</v>
+        <v>18605</v>
       </c>
       <c r="D6" t="n">
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="E6" t="n">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -612,6 +612,50 @@
       </c>
       <c r="F8" t="n">
         <v>261</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>49908</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1884</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22436</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E10" t="n">
+        <v>172</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11048.xlsx
+++ b/output/roomself_excel/11048.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2576</v>
       </c>
-      <c r="E2" t="n">
-        <v>431</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>241</v>
+        <v>401</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>220</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3188</v>
       </c>
-      <c r="E3" t="n">
-        <v>468</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>382</v>
+        <v>348</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>436</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>3044</v>
       </c>
-      <c r="E4" t="n">
-        <v>513</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>311</v>
+        <v>267</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +609,26 @@
       <c r="D5" t="n">
         <v>1624</v>
       </c>
-      <c r="E5" t="n">
-        <v>188</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>91</v>
+      </c>
+      <c r="J5" t="n">
         <v>37</v>
       </c>
     </row>
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>1160</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>70</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>30</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>820</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>108</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>30</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +707,27 @@
       <c r="D8" t="n">
         <v>1704</v>
       </c>
-      <c r="E8" t="n">
-        <v>273</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>261</v>
+        <v>528</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>153</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +745,12 @@
       <c r="D9" t="n">
         <v>1884</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +767,27 @@
       <c r="D10" t="n">
         <v>1200</v>
       </c>
-      <c r="E10" t="n">
-        <v>172</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49</v>
+      </c>
+      <c r="J10" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11048.xlsx
+++ b/output/roomself_excel/11048.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +557,26 @@
       <c r="J2" t="n">
         <v>30</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>154</v>
+      </c>
+      <c r="N2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +615,38 @@
       <c r="J3" t="n">
         <v>21</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>213</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>76</v>
+      </c>
+      <c r="R3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +685,38 @@
       <c r="J4" t="n">
         <v>31</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>179</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,6 +755,14 @@
       <c r="J5" t="n">
         <v>37</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +793,26 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +843,26 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -727,6 +899,38 @@
         <v>153</v>
       </c>
       <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>77</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>63</v>
+      </c>
+      <c r="R8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -751,6 +955,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -789,6 +1001,26 @@
       <c r="J10" t="n">
         <v>30</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
